--- a/data/WP17_beteiligte_ministerien.xlsx
+++ b/data/WP17_beteiligte_ministerien.xlsx
@@ -377,10 +377,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>6369</v>
+        <v>2729</v>
       </c>
       <c r="C2" t="n">
-        <v>33.1286926461346</v>
+        <v>30.1787812041116</v>
       </c>
       <c r="D2"/>
       <c r="E2"/>
@@ -390,10 +390,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>4323</v>
+        <v>1888</v>
       </c>
       <c r="C3" t="n">
-        <v>34.1433202130123</v>
+        <v>32.1714437367304</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -403,10 +403,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>2257</v>
+        <v>1315</v>
       </c>
       <c r="C4" t="n">
-        <v>33.5037694013305</v>
+        <v>30.1028179741051</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -416,16 +416,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>707</v>
+        <v>430</v>
       </c>
       <c r="C5" t="n">
-        <v>35.7920792079208</v>
+        <v>34.4697674418605</v>
       </c>
       <c r="D5" t="n">
-        <v>577</v>
+        <v>332</v>
       </c>
       <c r="E5" t="n">
-        <v>18.3875530410184</v>
+        <v>22.7906976744186</v>
       </c>
     </row>
     <row r="6">
@@ -433,16 +433,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>178</v>
+        <v>132</v>
       </c>
       <c r="C6" t="n">
-        <v>38.0674157303371</v>
+        <v>38.4090909090909</v>
       </c>
       <c r="D6" t="n">
-        <v>153</v>
+        <v>112</v>
       </c>
       <c r="E6" t="n">
-        <v>14.0449438202247</v>
+        <v>15.1515151515152</v>
       </c>
     </row>
     <row r="7">
@@ -450,16 +450,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>36.4782608695652</v>
+        <v>36.875</v>
       </c>
       <c r="D7" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>4.34782608695652</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="8">
@@ -730,13 +730,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3419D694-8651-485A-AAD9-057EEFF2C5B9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43AC00B8-2C46-4C1C-BDA4-6E837EC4F84A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58C77EFC-E1E3-4B33-9A0A-7FEFDA292C8D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6D64999-9B42-474B-B9F9-B5075FB6FA02}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29BD3CD5-4501-4023-AFAE-EC3EAB1C1637}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CFDCE0D-075D-414C-A9C2-A909556AD56A}"/>
 </file>